--- a/config/talent.xlsx
+++ b/config/talent.xlsx
@@ -1593,14 +1593,14 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
+          <t>基础天赋</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>基礎天賦</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>基礎天賦</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Basic talent</t>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>味方全員のHPと速度が上昇</t>
+          <t>我方全体人员的生命值和速度上升</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="T6" s="1" t="inlineStr">
         <is>
-          <t>速度上昇</t>
+          <t>速度上升</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1755,14 +1755,14 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
+          <t>基础天赋</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>基礎天賦</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>基礎天賦</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Basic talent</t>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>味方全員の物攻と特攻が上昇</t>
+          <t>我方全员的物攻和特攻上升</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>物攻上昇</t>
+          <t>物攻上升</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="T7" s="1" t="inlineStr">
         <is>
-          <t>特攻上昇</t>
+          <t>特攻上升</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1927,14 +1927,14 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
+          <t>基础天赋</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>基礎天賦</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>基礎天賦</t>
-        </is>
-      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Basic talent</t>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>味方全員の物防と特防が上昇</t>
+          <t>我方全员的物防和特防上升</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>物防上昇</t>
+          <t>物防上升</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="T8" s="1" t="inlineStr">
         <is>
-          <t>特防上昇</t>
+          <t>特防上升</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -2099,14 +2099,14 @@
       </c>
       <c r="B9" s="1" t="inlineStr">
         <is>
+          <t>基础天赋</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>基礎天賦</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>基礎天賦</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>Basic talent</t>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>戦闘中に前列味方のHPが上昇</t>
+          <t>战斗中前排我方的HP上升</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -2231,14 +2231,14 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>基础天赋</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>基礎天賦</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>基礎天賦</t>
-        </is>
-      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Basic talent</t>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>戦闘中に後列味方の物攻と特攻が上昇</t>
+          <t>战斗中后排我方的物攻和特攻上升</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>物攻上昇</t>
+          <t>物攻上升</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="T10" s="1" t="inlineStr">
         <is>
-          <t>特攻上昇</t>
+          <t>特攻上升</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -2403,14 +2403,14 @@
       </c>
       <c r="B11" s="1" t="inlineStr">
         <is>
+          <t>基础天赋</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>基礎天賦</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>基礎天賦</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Basic talent</t>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>戦闘中に後列味方のダメージが上昇</t>
+          <t>战斗中后排我方的伤害上升</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ダメージ上昇</t>
+          <t>伤害加成</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2535,14 +2535,14 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
+          <t>基础天赋</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>基礎天賦</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>基礎天賦</t>
-        </is>
-      </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Basic talent</t>
@@ -2570,7 +2570,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>戦闘中に前列味方のダメージ耐性が上昇</t>
+          <t>战斗中前排伙伴的伤害减免上升</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2595,7 +2595,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ダメージ耐性上昇</t>
+          <t>抗伤害能力上升</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B13" s="1" t="inlineStr">
         <is>
-          <t>突破天賦</t>
+          <t>突破天赋</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>味方全員のHPの初期値が上昇</t>
+          <t>我方全员的HP初始值上升</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>突破天賦</t>
+          <t>突破天赋</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>味方全員の物攻の初期値が上昇</t>
+          <t>我方全员的物攻初始值上升</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>物攻上昇</t>
+          <t>物攻上升</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="B15" s="1" t="inlineStr">
         <is>
-          <t>突破天賦</t>
+          <t>突破天赋</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>味方全員の特防の初期値が上昇</t>
+          <t>我方全员的特防初期值上升</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>特防上昇</t>
+          <t>特防上升</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>突破天賦</t>
+          <t>突破天赋</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>味方全員の会心耐性の初期値が上昇</t>
+          <t>全体伙伴的暴击抵抗的初始值上升</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3113,7 +3113,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>会心耐性上昇</t>
+          <t>暴击抵抗上升</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3185,7 +3185,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>突破天賦</t>
+          <t>突破天赋</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>味方全員の物攻の初期値が上昇</t>
+          <t>我方全员的物攻初始值上升</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3245,7 +3245,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>物防上昇</t>
+          <t>物防上升</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>突破天賦</t>
+          <t>突破天赋</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>味方全員の特攻の初期値が上昇</t>
+          <t>我方全员特攻的初期值上升</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>特攻上昇</t>
+          <t>特攻上升</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>突破天賦</t>
+          <t>突破天赋</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>味方全員の会心の初期値が上昇</t>
+          <t>我方全员会心的初始值上升</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>会心上昇</t>
+          <t>会心上升</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>突破天賦</t>
+          <t>突破天赋</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>味方全員のダメージ耐性の初期値が上昇</t>
+          <t>我方全体人员的伤害减免初始值上升</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3641,7 +3641,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>ダメージ耐性上昇</t>
+          <t>抗伤害能力上升</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>突破天賦</t>
+          <t>突破天赋</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>味方全員のダメージの初期値が上昇</t>
+          <t>我方全体人员的初始伤害值上升</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>ダメージ上昇</t>
+          <t>伤害加成</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>突破天賦</t>
+          <t>突破天赋</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>味方全員の速度の初期値が上昇</t>
+          <t>我方全体人员的速度初始值上升</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>速度上昇</t>
+          <t>速度上升</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>無属性の味方全員のHPが上昇</t>
+          <t>无属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -4109,7 +4109,7 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>味方全員の無属性スキルダメージが上昇</t>
+          <t>我方全员无属性技能伤害上升</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>無属性スキルダメージ上昇</t>
+          <t>无属性技能伤害上升</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>味方全員の無属性スキルダメージ耐性が上昇</t>
+          <t>我方全员无属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>無属性スキルダメージ耐性上昇</t>
+          <t>无属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>炎属性の味方全員のHPが上昇</t>
+          <t>炎属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>味方全員の炎属性スキルダメージが上昇</t>
+          <t>我方全员的火焰属性技能伤害上升</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>炎属性スキルダメージ上昇</t>
+          <t>火焰属性技能伤害上升</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>味方全員の炎属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的火焰属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>炎属性スキルダメージ耐性上昇</t>
+          <t>炎属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>水属性の味方全員のHPが上昇</t>
+          <t>水属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -4854,7 +4854,7 @@
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>味方全員の水属性スキルダメージが上昇</t>
+          <t>我方全员的水属性技能伤害上升</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>水属性スキルダメージ上昇</t>
+          <t>水属性技能伤害上升</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>味方全員の水属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的水属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>水属性スキルダメージ耐性上昇</t>
+          <t>水属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>木属性の味方全員のHPが上昇</t>
+          <t>木属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -5260,7 +5260,7 @@
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5367,7 +5367,7 @@
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>味方全員の木属性スキルダメージが上昇</t>
+          <t>我方全员的树属性技能伤害上升</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -5392,7 +5392,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>木属性スキルダメージ上昇</t>
+          <t>木属性技能伤害上升</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>味方全員の木属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的树属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>木属性スキルダメージ耐性上昇</t>
+          <t>木属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>雷属性の味方全員のHPが上昇</t>
+          <t>雷属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -5733,7 +5733,7 @@
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>味方全員の雷属性スキルダメージが上昇</t>
+          <t>我方全员的雷属性技能伤害上升</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>雷属性スキルダメージ上昇</t>
+          <t>雷属性技能伤害上升</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>味方全員の雷属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的雷属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -5935,7 +5935,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>雷属性スキルダメージ耐性上昇</t>
+          <t>雷属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>寒属性の味方全員のHPが上昇</t>
+          <t>寒属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -6179,7 +6179,7 @@
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>味方全員の寒属性スキルダメージが上昇</t>
+          <t>我方全员的寒属性技能伤害上升</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>寒属性スキルダメージ上昇</t>
+          <t>寒属性技能伤害上升</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>味方全員の寒属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的寒属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>寒属性スキルダメージ耐性上昇</t>
+          <t>寒属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>戦属性の味方全員のHPが上昇</t>
+          <t>战属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="O41" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -6545,7 +6545,7 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>味方全員の戦属性スキルダメージが上昇</t>
+          <t>我方全员的战属性技能伤害上升</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>戦属性スキルダメージ上昇</t>
+          <t>战斗属性技能伤害上升</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -6682,7 +6682,7 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>味方全員の戦属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的战属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>戦属性スキルダメージ耐性上昇</t>
+          <t>战斗属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>毒属性の味方全員のHPが上昇</t>
+          <t>毒属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="O44" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -6951,7 +6951,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>味方全員の毒属性スキルダメージが上昇</t>
+          <t>我方全员的毒属性技能伤害上升</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>毒属性スキルダメージ上昇</t>
+          <t>毒属性技能伤害上升</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -7128,7 +7128,7 @@
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>味方全員の毒属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的毒属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -7153,7 +7153,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>毒属性スキルダメージ耐性上昇</t>
+          <t>毒属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -7225,7 +7225,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7265,7 +7265,7 @@
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>地属性の味方全員のHPが上昇</t>
+          <t>地属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -7290,7 +7290,7 @@
       </c>
       <c r="O47" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>味方全員の地属性スキルダメージが上昇</t>
+          <t>我方全员的地属性技能伤害上升</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -7422,7 +7422,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>地属性スキルダメージ上昇</t>
+          <t>地属性技能伤害上升</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>味方全員の地属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的地属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>地属性スキルダメージ耐性上昇</t>
+          <t>地属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>空属性の味方全員のHPが上昇</t>
+          <t>空属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="O50" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>味方全員の空属性スキルダメージが上昇</t>
+          <t>我方全员的空属性技能伤害上升</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>空属性スキルダメージ上昇</t>
+          <t>空属性技能伤害上升</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>味方全員の空属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的空属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -7965,7 +7965,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>空属性スキルダメージ耐性上昇</t>
+          <t>空属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>法属性の味方全員のHPが上昇</t>
+          <t>法属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -8102,7 +8102,7 @@
       </c>
       <c r="O53" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -8209,7 +8209,7 @@
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>味方全員の法属性スキルダメージが上昇</t>
+          <t>我方全员的法属性技能伤害上升</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -8234,7 +8234,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>法属性スキルダメージ上昇</t>
+          <t>法属性技能伤害上升</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>味方全員の法属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的法属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>法属性スキルダメージ耐性上昇</t>
+          <t>法属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>魅属性の味方全員のHPが上昇</t>
+          <t>魅属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="O56" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -8575,7 +8575,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8615,7 +8615,7 @@
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>味方全員の魅属性スキルダメージが上昇</t>
+          <t>我方全员的魅属性技能伤害上升</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -8640,7 +8640,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>魅属性スキルダメージ上昇</t>
+          <t>魅属性技能伤害上升</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>味方全員の魅属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的魅属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>魅属性スキルダメージ耐性上昇</t>
+          <t>魅属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>岩属性の味方全員のHPが上昇</t>
+          <t>岩石属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O59" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -8981,7 +8981,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>味方全員の岩属性スキルダメージが上昇</t>
+          <t>我方全员的岩石属性技能伤害上升</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>岩属性スキルダメージ上昇</t>
+          <t>岩石属性技能伤害上升</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>味方全員の岩属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的岩石属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -9183,7 +9183,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>岩属性スキルダメージ耐性上昇</t>
+          <t>岩石属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>暗属性の味方全員のHPが上昇</t>
+          <t>暗属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -9320,7 +9320,7 @@
       </c>
       <c r="O62" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -9387,7 +9387,7 @@
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>味方全員の暗属性スキルダメージが上昇</t>
+          <t>我方全员的暗属性技能伤害上升</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>暗属性スキルダメージ耐性上昇</t>
+          <t>暗属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>味方全員の暗属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的暗属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>闇属性スキルダメージ耐性上昇</t>
+          <t>暗属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>神属性の味方全員のHPが上昇</t>
+          <t>神属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -9726,7 +9726,7 @@
       </c>
       <c r="O65" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -9793,7 +9793,7 @@
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>味方全員の神属性スキルダメージが上昇</t>
+          <t>我方全员的神属性技能伤害上升</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>神属性スキルダメージ上昇</t>
+          <t>神属性技能伤害上升</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -9930,7 +9930,7 @@
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -9970,7 +9970,7 @@
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>味方全員の神属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的神属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>神属性スキルダメージ耐性上昇</t>
+          <t>神属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>邪属性の味方全員のHPが上昇</t>
+          <t>邪属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -10132,7 +10132,7 @@
       </c>
       <c r="O68" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -10239,7 +10239,7 @@
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>味方全員の邪属性スキルダメージが上昇</t>
+          <t>我方全员的邪属性技能伤害上升</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>邪属性スキルダメージ上昇</t>
+          <t>邪属性技能伤害上升</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>味方全員の邪属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的邪属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>邪属性スキルダメージ耐性上昇</t>
+          <t>邪属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>金属性の味方全員のHPが上昇</t>
+          <t>所有金属性伙伴的HP上升</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -10538,7 +10538,7 @@
       </c>
       <c r="O71" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10645,7 +10645,7 @@
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>味方全員の金属性スキルダメージが上昇</t>
+          <t>我方全员的金属技能伤害上升</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -10670,7 +10670,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>金属性スキルダメージ上昇</t>
+          <t>金属技能伤害上升</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -10742,7 +10742,7 @@
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -10782,7 +10782,7 @@
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>味方全員の金属性スキルダメージ耐性が上昇</t>
+          <t>我方全体人员的金属技能伤害减免上升</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>金属性スキルダメージ耐性上昇</t>
+          <t>金属技能伤害减免上升</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>精属性の味方全員のHPが上昇</t>
+          <t>精属性的伙伴全体的HP上升</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="O74" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>味方全員の精属性スキルダメージが上昇</t>
+          <t>我方全员精属性技能伤害上升</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>精属性スキルダメージ上昇</t>
+          <t>精属性技能伤害上升</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>仲間天賦</t>
+          <t>伙伴天赋</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>味方全員の精属性スキルダメージ耐性が上昇</t>
+          <t>我方全员的精属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>精属性スキルダメージ耐性上昇</t>
+          <t>精属性技能伤害减免上升</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>アリーナ</t>
+          <t>竞技场</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>アリーナで味方のHPが上昇</t>
+          <t>竞技场中我方的HP上升</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -11345,7 +11345,7 @@
       </c>
       <c r="O77" s="1" t="inlineStr">
         <is>
-          <t>HP上昇</t>
+          <t>HP上升</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -11417,7 +11417,7 @@
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>アリーナ</t>
+          <t>竞技场</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>アリーナで味方の戦闘能力が上昇</t>
+          <t>竞技场中我方战斗能力上升</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="O78" s="1" t="inlineStr">
         <is>
-          <t>ダメージ上昇</t>
+          <t>伤害加成</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="T78" s="1" t="inlineStr">
         <is>
-          <t>ダメージ耐性上昇</t>
+          <t>抗伤害能力上升</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>アリーナ</t>
+          <t>竞技场</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>アリーナで味方の戦闘能力が上昇</t>
+          <t>竞技场中我方战斗能力上升</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="O79" s="1" t="inlineStr">
         <is>
-          <t>スキルダメージ上昇</t>
+          <t>技能伤害上升</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -11684,7 +11684,7 @@
       </c>
       <c r="T79" s="1" t="inlineStr">
         <is>
-          <t>スキルダメージ耐性上昇</t>
+          <t>技能伤害减免上升</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
